--- a/slide_classification/TCGA_Results/Averaging/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -514,10 +514,10 @@
         <v>9e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.306196</v>
+        <v>0.64478</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.930191</v>
+        <v>0.890371</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.165951</v>
+        <v>0.166277</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.858282</v>
+        <v>0.900158</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.339286</v>
+        <v>0.170682</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.809073</v>
+        <v>0.834723</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.634875</v>
+        <v>0.671674</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.347572</v>
+        <v>0.203991</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -858,10 +858,10 @@
         <v>0.010895</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.679626</v>
+        <v>0.411853</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.163319</v>
+        <v>0.124964</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.998431</v>
+        <v>0.999484</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -987,10 +987,10 @@
         <v>0.011765</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7431</v>
+        <v>0.465875</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.380441</v>
+        <v>0.25566</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.22091</v>
+        <v>0.184914</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         <v>0.131874</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.427032</v>
+        <v>0.522769</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.263043</v>
+        <v>0.181112</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.246468</v>
+        <v>0.137195</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.167181</v>
+        <v>0.136858</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.231027</v>
+        <v>0.155218</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.214298</v>
+        <v>0.185357</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.666377</v>
+        <v>0.7212229999999999</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1962</v>
+        <v>0.194114</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.291872</v>
+        <v>0.233362</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.277242</v>
+        <v>0.242436</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.275321</v>
+        <v>0.263757</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.354067</v>
+        <v>0.37837</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.222472</v>
+        <v>0.232208</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.37318</v>
+        <v>0.263933</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.955213</v>
+        <v>0.870221</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.315592</v>
+        <v>0.265028</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.269558</v>
+        <v>0.294006</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.359698</v>
+        <v>0.391112</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.891857</v>
+        <v>0.875762</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1933,10 +1933,10 @@
         <v>0.085995</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.503916</v>
+        <v>0.394329</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.347653</v>
+        <v>0.353431</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.306875</v>
+        <v>0.265204</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.36601</v>
+        <v>0.336966</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.465842</v>
+        <v>0.429083</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.466317</v>
+        <v>0.471714</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.272836</v>
+        <v>0.158234</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.174536</v>
+        <v>0.164993</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.157786</v>
+        <v>0.131464</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.369189</v>
+        <v>0.383785</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.583742</v>
+        <v>0.553854</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.324673</v>
+        <v>0.459755</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.267688</v>
+        <v>0.368159</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2492,10 +2492,10 @@
         <v>0.009153</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.551338</v>
+        <v>0.344933</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.778742</v>
+        <v>0.823751</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.28475</v>
+        <v>0.229743</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.321385</v>
+        <v>0.235758</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.917057</v>
+        <v>0.9943650000000001</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.399975</v>
+        <v>0.154877</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.407156</v>
+        <v>0.323817</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.406493</v>
+        <v>0.249687</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.224092</v>
+        <v>0.2055</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0.703552</v>
+        <v>0.656574</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.354607</v>
+        <v>0.216673</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.699775</v>
+        <v>0.872772</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.708369</v>
+        <v>0.647961</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.964943</v>
+        <v>0.942496</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.296926</v>
+        <v>0.194491</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.919323</v>
+        <v>0.927721</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.270435</v>
+        <v>0.2277</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.353186</v>
+        <v>0.312496</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.335629</v>
+        <v>0.249449</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.319553</v>
+        <v>0.362429</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.435528</v>
+        <v>0.384253</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.497224</v>
+        <v>0.383287</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.296895</v>
+        <v>0.404525</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3481,10 +3481,10 @@
         <v>0.52954</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.474864</v>
+        <v>0.683208</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.300113</v>
+        <v>0.334886</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3567,10 +3567,10 @@
         <v>0.035297</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.45597</v>
+        <v>0.556485</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.291614</v>
+        <v>0.188812</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.355399</v>
+        <v>0.237065</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.4183</v>
+        <v>0.28522</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.822457</v>
+        <v>0.935708</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.400626</v>
+        <v>0.336743</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.523145</v>
+        <v>0.5947440000000001</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3868,10 +3868,10 @@
         <v>0.008247000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.401243</v>
+        <v>0.53839</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3911,10 +3911,10 @@
         <v>0.056631</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.53923</v>
+        <v>0.338505</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.63393</v>
+        <v>0.566999</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3997,10 +3997,10 @@
         <v>0.041797</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.6353</v>
+        <v>0.419005</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4040,10 +4040,10 @@
         <v>0.000149</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.672693</v>
+        <v>0.343486</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.252198</v>
+        <v>0.28786</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.781918</v>
+        <v>0.661686</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.358565</v>
+        <v>0.278025</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.419251</v>
+        <v>0.094753</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.781</v>
+        <v>0.789981</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.17842</v>
+        <v>0.115807</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.464478</v>
+        <v>0.207195</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.360169</v>
+        <v>0.238158</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.487038</v>
+        <v>0.336351</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.354794</v>
+        <v>0.235571</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.554416</v>
+        <v>0.553647</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0.075861</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.556686</v>
+        <v>0.386808</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.33624</v>
+        <v>0.236273</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.736704</v>
+        <v>0.690195</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.7947650000000001</v>
+        <v>0.834516</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.349555</v>
+        <v>0.325869</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.828301</v>
+        <v>0.631059</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.866754</v>
+        <v>0.663168</v>
       </c>
       <c r="H102" t="n">
         <v>1</v>
@@ -4857,10 +4857,10 @@
         <v>0.049999</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.505092</v>
+        <v>0.400462</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.374587</v>
+        <v>0.34585</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.295146</v>
+        <v>0.152091</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9157,10 +9157,10 @@
         <v>0.011674</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.447544</v>
+        <v>0.634344</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0.368547</v>
+        <v>0.308046</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.271963</v>
+        <v>0.079813</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.873027</v>
+        <v>0.904627</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>0.426255</v>
+        <v>0.377562</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.335238</v>
+        <v>0.343827</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.335232</v>
+        <v>0.229055</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.739313</v>
+        <v>0.719286</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.224094</v>
+        <v>0.120454</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.437849</v>
+        <v>0.365551</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9587,10 +9587,10 @@
         <v>0.051445</v>
       </c>
       <c r="F213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.50774</v>
+        <v>0.289215</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.320638</v>
+        <v>0.220634</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9673,10 +9673,10 @@
         <v>0.008057999999999999</v>
       </c>
       <c r="F215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.551535</v>
+        <v>0.182971</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0.520562</v>
+        <v>0.648958</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.27192</v>
+        <v>0.101625</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9805,7 +9805,7 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.374801</v>
+        <v>0.341503</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.415603</v>
+        <v>0.124498</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.409524</v>
+        <v>0.323087</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.395541</v>
+        <v>0.174363</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>0.479093</v>
+        <v>0.325993</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.446337</v>
+        <v>0.402357</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.487978</v>
+        <v>0.275907</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10103,10 +10103,10 @@
         <v>0.020434</v>
       </c>
       <c r="F225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.549812</v>
+        <v>0.494047</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.483752</v>
+        <v>0.433663</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.474974</v>
+        <v>0.493333</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.413808</v>
+        <v>0.224382</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.34152</v>
+        <v>0.239363</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.443004</v>
+        <v>0.285116</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.674506</v>
+        <v>0.665855</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.492603</v>
+        <v>0.429127</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0.790902</v>
+        <v>0.995421</v>
       </c>
       <c r="H233" t="n">
         <v>1</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.317354</v>
+        <v>0.221205</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>0.292278</v>
+        <v>0.117393</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.447542</v>
+        <v>0.246984</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.368443</v>
+        <v>0.143259</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10662,10 +10662,10 @@
         <v>0.020522</v>
       </c>
       <c r="F238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.506122</v>
+        <v>0.41239</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.423181</v>
+        <v>0.191373</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.321199</v>
+        <v>0.147379</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.421312</v>
+        <v>0.319095</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.332644</v>
+        <v>0.143765</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0.025946</v>
       </c>
       <c r="F243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.514055</v>
+        <v>0.36207</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>0.43855</v>
+        <v>0.455253</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.742645</v>
+        <v>0.974858</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.807907</v>
+        <v>0.856593</v>
       </c>
       <c r="H246" t="n">
         <v>1</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.8981170000000001</v>
+        <v>0.992526</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -11092,10 +11092,10 @@
         <v>0.267781</v>
       </c>
       <c r="F248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.423462</v>
+        <v>0.506495</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.887477</v>
+        <v>0.9987780000000001</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.39525</v>
+        <v>0.160571</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.344871</v>
+        <v>0.274732</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.7282189999999999</v>
+        <v>0.826821</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.152292</v>
+        <v>0.08171399999999999</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.485632</v>
+        <v>0.248983</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="G255" t="n">
-        <v>0.758664</v>
+        <v>0.9978320000000001</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.661684</v>
+        <v>0.913513</v>
       </c>
       <c r="H256" t="n">
         <v>1</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.692638</v>
+        <v>0.576928</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.957379</v>
+        <v>0.972559</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11565,10 +11565,10 @@
         <v>0.6790659999999999</v>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.493868</v>
+        <v>0.512094</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.228551</v>
+        <v>0.13853</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>0.319529</v>
+        <v>0.244433</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11694,10 +11694,10 @@
         <v>0.7078759999999999</v>
       </c>
       <c r="F262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0.534784</v>
+        <v>0.341252</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.472111</v>
+        <v>0.433487</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.623657</v>
+        <v>0.7907690000000001</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.324689</v>
+        <v>0.235804</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.191073</v>
+        <v>0.174457</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.5620849999999999</v>
+        <v>0.838075</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>0</v>
       </c>
       <c r="G268" t="n">
-        <v>0.465065</v>
+        <v>0.433053</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.339444</v>
+        <v>0.228147</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.422504</v>
+        <v>0.362739</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.383218</v>
+        <v>0.157628</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12124,10 +12124,10 @@
         <v>0.013218</v>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0.520366</v>
+        <v>0.312836</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>0.426555</v>
+        <v>0.319645</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>0.675455</v>
+        <v>0.799854</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.276405</v>
+        <v>0.182411</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>0.637186</v>
+        <v>0.88801</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.434048</v>
+        <v>0.307284</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>1</v>
       </c>
       <c r="G278" t="n">
-        <v>0.519773</v>
+        <v>0.595032</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0.609287</v>
+        <v>0.765498</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.234313</v>
+        <v>0.143097</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.482555</v>
+        <v>0.423711</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.201428</v>
+        <v>0.220449</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.281865</v>
+        <v>0.191371</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.344375</v>
+        <v>0.211016</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.496366</v>
+        <v>0.279332</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>1</v>
       </c>
       <c r="G286" t="n">
-        <v>0.718984</v>
+        <v>0.845909</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12769,10 +12769,10 @@
         <v>0.009709000000000001</v>
       </c>
       <c r="F287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0.446754</v>
+        <v>0.7946800000000001</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.40428</v>
+        <v>0.296937</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.291035</v>
+        <v>0.166826</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.249944</v>
+        <v>0.210475</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.423118</v>
+        <v>0.334571</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.252639</v>
+        <v>0.29352</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0.507065</v>
+        <v>0.596693</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.259722</v>
+        <v>0.166056</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.224059</v>
+        <v>0.13708</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.962722</v>
+        <v>0.999995</v>
       </c>
       <c r="H296" t="n">
         <v>1</v>
@@ -13202,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="G297" t="n">
-        <v>0.439871</v>
+        <v>0.378909</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.401412</v>
+        <v>0.348143</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0.5352749999999999</v>
+        <v>0.516861</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>0.414946</v>
+        <v>0.259989</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.290791</v>
+        <v>0.18331</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.496753</v>
+        <v>0.314292</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.749257</v>
+        <v>0.976057</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.77371</v>
+        <v>0.9286799999999999</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13543,10 +13543,10 @@
         <v>0.004183</v>
       </c>
       <c r="F305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.567906</v>
+        <v>0.451285</v>
       </c>
       <c r="H305" t="n">
         <v>1</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.424508</v>
+        <v>0.428333</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0.486763</v>
+        <v>0.458367</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13672,10 +13672,10 @@
         <v>0.323379</v>
       </c>
       <c r="F308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0.493298</v>
+        <v>0.520461</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.7077020000000001</v>
+        <v>0.875897</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.361996</v>
+        <v>0.229632</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>0.699972</v>
+        <v>0.7020149999999999</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.183255</v>
+        <v>0.068471</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.289294</v>
+        <v>0.159535</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.40134</v>
+        <v>0.130396</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.415503</v>
+        <v>0.123415</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.342554</v>
+        <v>0.091359</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.391764</v>
+        <v>0.135409</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0.414765</v>
+        <v>0.409116</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14145,10 +14145,10 @@
         <v>0.001544</v>
       </c>
       <c r="F319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.523889</v>
+        <v>0.34928</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0.766617</v>
+        <v>0.91173</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.354697</v>
+        <v>0.185174</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>1</v>
       </c>
       <c r="G322" t="n">
-        <v>0.690376</v>
+        <v>0.6336349999999999</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.36854</v>
+        <v>0.155947</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.435504</v>
+        <v>0.089032</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.419428</v>
+        <v>0.15749</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14446,10 +14446,10 @@
         <v>0.07103</v>
       </c>
       <c r="F326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.528271</v>
+        <v>0.233869</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14489,10 +14489,10 @@
         <v>0.037742</v>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.505504</v>
+        <v>0.366347</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14532,10 +14532,10 @@
         <v>0.08182300000000001</v>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G328" t="n">
-        <v>0.641605</v>
+        <v>0.485547</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.337569</v>
+        <v>0.161453</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.429279</v>
+        <v>0.09991800000000001</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.7373459999999999</v>
+        <v>0.796553</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.4563</v>
+        <v>0.232895</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.883501</v>
+        <v>0.998889</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.444286</v>
+        <v>0.367811</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.42902</v>
+        <v>0.243211</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.316479</v>
+        <v>0.324945</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.369967</v>
+        <v>0.162114</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.215758</v>
+        <v>0.053427</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.423373</v>
+        <v>0.153194</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15048,10 +15048,10 @@
         <v>0.006534</v>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.532744</v>
+        <v>0.17091</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.483425</v>
+        <v>0.209519</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.26581</v>
+        <v>0.0731</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.408894</v>
+        <v>0.153704</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.354556</v>
+        <v>0.087668</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15263,10 +15263,10 @@
         <v>0.006395</v>
       </c>
       <c r="F345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.566761</v>
+        <v>0.305557</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.423098</v>
+        <v>0.182367</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15349,10 +15349,10 @@
         <v>0.00433</v>
       </c>
       <c r="F347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.506837</v>
+        <v>0.309612</v>
       </c>
       <c r="H347" t="n">
         <v>1</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.348072</v>
+        <v>0.238834</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0.75388</v>
+        <v>0.995893</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>0.430311</v>
+        <v>0.293131</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.387936</v>
+        <v>0.071382</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15564,10 +15564,10 @@
         <v>0.004066</v>
       </c>
       <c r="F352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.540865</v>
+        <v>0.342824</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.273332</v>
+        <v>0.057233</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.24261</v>
+        <v>0.094843</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.29552</v>
+        <v>0.09131499999999999</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.2843</v>
+        <v>0.161706</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.209036</v>
+        <v>0.060852</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15822,10 +15822,10 @@
         <v>0.121289</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.45429</v>
+        <v>0.91213</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.26277</v>
+        <v>0.057349</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0.619583</v>
+        <v>0.563906</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.396419</v>
+        <v>0.318672</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15994,10 +15994,10 @@
         <v>0.005067</v>
       </c>
       <c r="F362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G362" t="n">
-        <v>0.568005</v>
+        <v>0.424083</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.343246</v>
+        <v>0.163276</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16080,10 +16080,10 @@
         <v>0.009519</v>
       </c>
       <c r="F364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>0.514439</v>
+        <v>0.222118</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.380741</v>
+        <v>0.172592</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.456497</v>
+        <v>0.216236</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.344763</v>
+        <v>0.199441</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.369433</v>
+        <v>0.214808</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16295,10 +16295,10 @@
         <v>9.399999999999999e-05</v>
       </c>
       <c r="F369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.503974</v>
+        <v>0.136773</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.361027</v>
+        <v>0.271659</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>0</v>
       </c>
       <c r="G371" t="n">
-        <v>0.481606</v>
+        <v>0.166609</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.428601</v>
+        <v>0.322371</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.337602</v>
+        <v>0.139302</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.398399</v>
+        <v>0.263045</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.345242</v>
+        <v>0.155233</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>1</v>
       </c>
       <c r="G376" t="n">
-        <v>0.763533</v>
+        <v>0.6749540000000001</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16639,10 +16639,10 @@
         <v>0.102182</v>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.64841</v>
+        <v>0.20785</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.435283</v>
+        <v>0.243719</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.44812</v>
+        <v>0.345077</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>0</v>
       </c>
       <c r="G380" t="n">
-        <v>0.485917</v>
+        <v>0.169794</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.312908</v>
+        <v>0.479198</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16854,10 +16854,10 @@
         <v>0.001381</v>
       </c>
       <c r="F382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0.547642</v>
+        <v>0.219077</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.372394</v>
+        <v>0.230573</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.439783</v>
+        <v>0.119753</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.241882</v>
+        <v>0.099873</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.274468</v>
+        <v>0.124415</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.439801</v>
+        <v>0.468328</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.367056</v>
+        <v>0.105185</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17155,10 +17155,10 @@
         <v>0.000233</v>
       </c>
       <c r="F389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.501435</v>
+        <v>0.180362</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.441063</v>
+        <v>0.082492</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.425193</v>
+        <v>0.24466</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.490417</v>
+        <v>0.365796</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.653382</v>
+        <v>0.639776</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.324346</v>
+        <v>0.205582</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.776771</v>
+        <v>0.969015</v>
       </c>
       <c r="H395" t="n">
         <v>1</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.386755</v>
+        <v>0.218464</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0.58585</v>
+        <v>0.735725</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.476828</v>
+        <v>0.37081</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.462084</v>
+        <v>0.431478</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.289653</v>
+        <v>0.185927</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17671,10 +17671,10 @@
         <v>0.625725</v>
       </c>
       <c r="F401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.5972499999999999</v>
+        <v>0.426201</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.379873</v>
+        <v>0.407561</v>
       </c>
       <c r="H402" t="n">
         <v>1</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.751588</v>
+        <v>0.737606</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.451846</v>
+        <v>0.182002</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.371454</v>
+        <v>0.180787</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.392904</v>
+        <v>0.164698</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>0</v>
       </c>
       <c r="G407" t="n">
-        <v>0.485977</v>
+        <v>0.262515</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17972,10 +17972,10 @@
         <v>0.160942</v>
       </c>
       <c r="F408" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G408" t="n">
-        <v>0.647862</v>
+        <v>0.270728</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.425012</v>
+        <v>0.282329</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.267827</v>
+        <v>0.09858</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>0.454411</v>
+        <v>0.320269</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>0.344895</v>
+        <v>0.10588</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.291442</v>
+        <v>0.136399</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.909927</v>
+        <v>0.981005</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
